--- a/multclass_double_elimination/(30人)配布印刷・手作業用2classDoubleElimination.xlsx
+++ b/multclass_double_elimination/(30人)配布印刷・手作業用2classDoubleElimination.xlsx
@@ -1511,7 +1511,7 @@
         <is>
           <t>B
 MAIN
-13・14名</t>
+14名</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
         <is>
           <t>B
 MAIN
-13・14名</t>
+14名</t>
         </is>
       </c>
     </row>
